--- a/artfynd/A 47955-2022 artfynd.xlsx
+++ b/artfynd/A 47955-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47955-2022 artfynd.xlsx
+++ b/artfynd/A 47955-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104376601</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504737.1120364519</v>
+        <v>504737</v>
       </c>
       <c r="R2" t="n">
-        <v>7189412.072121724</v>
+        <v>7189412</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -813,15 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104377852</v>
+        <v>104377342</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,35 +819,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borgafjäll , Ås lm</t>
+          <t>Borgafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504760.6257336958</v>
+        <v>504643</v>
       </c>
       <c r="R3" t="n">
-        <v>7189370.380448543</v>
+        <v>7189396</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammalt exemplar men typisk röta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -951,15 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104376475</v>
+        <v>104377588</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,21 +957,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -992,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504510.7900249459</v>
+        <v>504720</v>
       </c>
       <c r="R4" t="n">
-        <v>7189375.956264338</v>
+        <v>7189344</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1027,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1037,7 +1027,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla exemplar men typisk röta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1089,15 +1084,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104377204</v>
+        <v>104376721</v>
       </c>
       <c r="B5" t="n">
-        <v>90560</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,10 +1120,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504686</v>
+        <v>504737</v>
       </c>
       <c r="R5" t="n">
-        <v>7189384</v>
+        <v>7189412</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1165,7 +1155,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1175,7 +1165,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1227,15 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104377243</v>
+        <v>104377204</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,35 +1228,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Borgafjäll, Ås lm</t>
+          <t>Borgafjäll , Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504685.5705295613</v>
+        <v>504686</v>
       </c>
       <c r="R6" t="n">
-        <v>7189384.314071692</v>
+        <v>7189384</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1303,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1313,7 +1298,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,37 +1350,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104376721</v>
+        <v>104377852</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1406,10 +1386,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504737.1120364519</v>
+        <v>504761</v>
       </c>
       <c r="R7" t="n">
-        <v>7189412.072121724</v>
+        <v>7189370</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1441,7 +1421,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1451,7 +1431,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1503,15 +1483,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104377759</v>
+        <v>104377936</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,35 +1494,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Borgafjäll , Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504760.6257336958</v>
+        <v>504857</v>
       </c>
       <c r="R8" t="n">
-        <v>7189370.380448543</v>
+        <v>7189324</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1579,7 +1559,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1589,7 +1569,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Relativt färska spår efter födosök</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1618,12 +1603,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1638,430 +1623,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>104377342</v>
-      </c>
-      <c r="B9" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Borgafjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>504643.3467321651</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7189395.745242817</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gammalt exemplar men typisk röta</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>104376500</v>
-      </c>
-      <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Borgafjäll , Ås lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>504676.9459576567</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7189447.319177523</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>104377588</v>
-      </c>
-      <c r="B11" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Borgafjäll , Ås lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>504720.1662858728</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7189343.916436208</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-10-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla exemplar men typisk röta</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47955-2022 artfynd.xlsx
+++ b/artfynd/A 47955-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104376601</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -943,6 +953,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104377342</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1081,6 +1096,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104377588</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1214,6 +1234,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104376721</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1347,6 +1372,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104377204</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1480,6 +1510,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104377852</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1623,8 +1658,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104377936</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>